--- a/data/titles.xlsx
+++ b/data/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D53"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,10 +421,10 @@
         <v>2026-01-04</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=da200abba3294df773d4bbae152092a1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=fdb0ba43c1da9b6f9914d4a562bf797a</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
     </row>
     <row r="3">
@@ -435,10 +435,10 @@
         <v>2026-01-04</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=da200abba3294df773d4bbae152092a1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=fdb0ba43c1da9b6f9914d4a562bf797a</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
     </row>
     <row r="4">
@@ -449,10 +449,10 @@
         <v>2026-01-04</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=da200abba3294df773d4bbae152092a1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=fdb0ba43c1da9b6f9914d4a562bf797a</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
     </row>
     <row r="5">
@@ -463,10 +463,10 @@
         <v>2026-01-04</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=da200abba3294df773d4bbae152092a1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=fdb0ba43c1da9b6f9914d4a562bf797a</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
     </row>
     <row r="6">
@@ -477,10 +477,10 @@
         <v>2026-01-04</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=da200abba3294df773d4bbae152092a1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=fdb0ba43c1da9b6f9914d4a562bf797a</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
     </row>
     <row r="7">
@@ -491,10 +491,10 @@
         <v>2026-01-04</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=da200abba3294df773d4bbae152092a1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=fdb0ba43c1da9b6f9914d4a562bf797a</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
     </row>
     <row r="8">
@@ -505,10 +505,10 @@
         <v>2026-01-04</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=da200abba3294df773d4bbae152092a1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=fdb0ba43c1da9b6f9914d4a562bf797a</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
     </row>
     <row r="9">
@@ -519,10 +519,10 @@
         <v>2026-01-04</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=da200abba3294df773d4bbae152092a1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=fdb0ba43c1da9b6f9914d4a562bf797a</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
     </row>
     <row r="10">
@@ -533,10 +533,10 @@
         <v>2026-01-04</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409056&amp;sid=da200abba3294df773d4bbae152092a1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409056&amp;sid=fdb0ba43c1da9b6f9914d4a562bf797a</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
     </row>
     <row r="11">
@@ -547,10 +547,10 @@
         <v>2026-01-04</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409055&amp;sid=da200abba3294df773d4bbae152092a1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409055&amp;sid=fdb0ba43c1da9b6f9914d4a562bf797a</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
     </row>
     <row r="12">
@@ -561,10 +561,10 @@
         <v>2026-01-04</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409054&amp;sid=da200abba3294df773d4bbae152092a1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409054&amp;sid=fdb0ba43c1da9b6f9914d4a562bf797a</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
     </row>
     <row r="13">
@@ -575,10 +575,10 @@
         <v>2026-01-04</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409053&amp;sid=da200abba3294df773d4bbae152092a1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409053&amp;sid=fdb0ba43c1da9b6f9914d4a562bf797a</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
     </row>
     <row r="14">
@@ -589,10 +589,10 @@
         <v>2026-01-04</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409052&amp;sid=da200abba3294df773d4bbae152092a1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409052&amp;sid=fdb0ba43c1da9b6f9914d4a562bf797a</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
     </row>
     <row r="15">
@@ -603,10 +603,10 @@
         <v>2026-01-03</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409038&amp;sid=da200abba3294df773d4bbae152092a1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409038&amp;sid=fdb0ba43c1da9b6f9914d4a562bf797a</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
     </row>
     <row r="16">
@@ -617,10 +617,10 @@
         <v>2026-01-03</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409037&amp;sid=da200abba3294df773d4bbae152092a1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409037&amp;sid=fdb0ba43c1da9b6f9914d4a562bf797a</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
     </row>
     <row r="17">
@@ -631,10 +631,10 @@
         <v>2026-01-03</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409036&amp;sid=da200abba3294df773d4bbae152092a1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409036&amp;sid=fdb0ba43c1da9b6f9914d4a562bf797a</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
     </row>
     <row r="18">
@@ -645,10 +645,10 @@
         <v>2026-01-03</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409035&amp;sid=da200abba3294df773d4bbae152092a1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409035&amp;sid=fdb0ba43c1da9b6f9914d4a562bf797a</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
     </row>
     <row r="19">
@@ -659,10 +659,10 @@
         <v>2026-01-01</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409025&amp;sid=da200abba3294df773d4bbae152092a1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409025&amp;sid=fdb0ba43c1da9b6f9914d4a562bf797a</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
     </row>
     <row r="20">
@@ -673,10 +673,10 @@
         <v>2026-01-01</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409024&amp;sid=da200abba3294df773d4bbae152092a1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409024&amp;sid=fdb0ba43c1da9b6f9914d4a562bf797a</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
     </row>
     <row r="21">
@@ -687,10 +687,10 @@
         <v>2026-01-01</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409023&amp;sid=da200abba3294df773d4bbae152092a1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409023&amp;sid=fdb0ba43c1da9b6f9914d4a562bf797a</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
     </row>
     <row r="22">
@@ -701,10 +701,10 @@
         <v>2026-01-01</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409022&amp;sid=da200abba3294df773d4bbae152092a1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409022&amp;sid=fdb0ba43c1da9b6f9914d4a562bf797a</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
     </row>
     <row r="23">
@@ -715,10 +715,10 @@
         <v>2026-01-01</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409021&amp;sid=da200abba3294df773d4bbae152092a1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409021&amp;sid=fdb0ba43c1da9b6f9914d4a562bf797a</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
     </row>
     <row r="24">
@@ -729,10 +729,10 @@
         <v>2026-01-01</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409020&amp;sid=da200abba3294df773d4bbae152092a1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409020&amp;sid=fdb0ba43c1da9b6f9914d4a562bf797a</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
     </row>
     <row r="25">
@@ -743,10 +743,10 @@
         <v>2026-01-01</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409019&amp;sid=da200abba3294df773d4bbae152092a1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409019&amp;sid=fdb0ba43c1da9b6f9914d4a562bf797a</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
     </row>
     <row r="26">
@@ -757,10 +757,10 @@
         <v>2026-01-01</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409018&amp;sid=da200abba3294df773d4bbae152092a1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409018&amp;sid=fdb0ba43c1da9b6f9914d4a562bf797a</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
     </row>
     <row r="27">
@@ -771,15 +771,379 @@
         <v>2026-01-01</v>
       </c>
       <c r="C27" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409017&amp;sid=fdb0ba43c1da9b6f9914d4a562bf797a</v>
+      </c>
+      <c r="D27" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>שריי אדר &amp; אודימן - הבל הבלים</v>
+      </c>
+      <c r="B28" t="str">
+        <v>2026-01-04</v>
+      </c>
+      <c r="C28" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=da200abba3294df773d4bbae152092a1</v>
+      </c>
+      <c r="D28" t="str">
+        <v>2026-01-04</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>שירז אברהם - היית לי עיניים</v>
+      </c>
+      <c r="B29" t="str">
+        <v>2026-01-04</v>
+      </c>
+      <c r="C29" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=da200abba3294df773d4bbae152092a1</v>
+      </c>
+      <c r="D29" t="str">
+        <v>2026-01-04</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>שייה - לפח</v>
+      </c>
+      <c r="B30" t="str">
+        <v>2026-01-04</v>
+      </c>
+      <c r="C30" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=da200abba3294df773d4bbae152092a1</v>
+      </c>
+      <c r="D30" t="str">
+        <v>2026-01-04</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>רותם כהן - לשרוף</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2026-01-04</v>
+      </c>
+      <c r="C31" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=da200abba3294df773d4bbae152092a1</v>
+      </c>
+      <c r="D31" t="str">
+        <v>2026-01-04</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>קלימה - תודה בורא עולם</v>
+      </c>
+      <c r="B32" t="str">
+        <v>2026-01-04</v>
+      </c>
+      <c r="C32" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=da200abba3294df773d4bbae152092a1</v>
+      </c>
+      <c r="D32" t="str">
+        <v>2026-01-04</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>דוד ברג - אזמרה</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2026-01-04</v>
+      </c>
+      <c r="C33" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=da200abba3294df773d4bbae152092a1</v>
+      </c>
+      <c r="D33" t="str">
+        <v>2026-01-04</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>אבירם פרחן - בגדו בי</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2026-01-04</v>
+      </c>
+      <c r="C34" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=da200abba3294df773d4bbae152092a1</v>
+      </c>
+      <c r="D34" t="str">
+        <v>2026-01-04</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>ניסן כהן - מה שלא תרצי</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2026-01-04</v>
+      </c>
+      <c r="C35" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=da200abba3294df773d4bbae152092a1</v>
+      </c>
+      <c r="D35" t="str">
+        <v>2026-01-04</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>מני חן - תני סימן קטן לאהבה</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2026-01-04</v>
+      </c>
+      <c r="C36" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409056&amp;sid=da200abba3294df773d4bbae152092a1</v>
+      </c>
+      <c r="D36" t="str">
+        <v>2026-01-04</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>ירין מסס - נדבר באהבה</v>
+      </c>
+      <c r="B37" t="str">
+        <v>2026-01-04</v>
+      </c>
+      <c r="C37" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409055&amp;sid=da200abba3294df773d4bbae152092a1</v>
+      </c>
+      <c r="D37" t="str">
+        <v>2026-01-04</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>חן ביטון - התקרבתי</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2026-01-04</v>
+      </c>
+      <c r="C38" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409054&amp;sid=da200abba3294df773d4bbae152092a1</v>
+      </c>
+      <c r="D38" t="str">
+        <v>2026-01-04</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>החצר האחורית של ג'וני - הזקן</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2026-01-04</v>
+      </c>
+      <c r="C39" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409053&amp;sid=da200abba3294df773d4bbae152092a1</v>
+      </c>
+      <c r="D39" t="str">
+        <v>2026-01-04</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>אליה נרקיס - שכחת את הכל</v>
+      </c>
+      <c r="B40" t="str">
+        <v>2026-01-04</v>
+      </c>
+      <c r="C40" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409052&amp;sid=da200abba3294df773d4bbae152092a1</v>
+      </c>
+      <c r="D40" t="str">
+        <v>2026-01-04</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>מיכאל סימן טוב - האחת מכולן</v>
+      </c>
+      <c r="B41" t="str">
+        <v>2026-01-03</v>
+      </c>
+      <c r="C41" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409038&amp;sid=da200abba3294df773d4bbae152092a1</v>
+      </c>
+      <c r="D41" t="str">
+        <v>2026-01-04</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>חביב חיים בן אריה - ותזרח</v>
+      </c>
+      <c r="B42" t="str">
+        <v>2026-01-03</v>
+      </c>
+      <c r="C42" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409037&amp;sid=da200abba3294df773d4bbae152092a1</v>
+      </c>
+      <c r="D42" t="str">
+        <v>2026-01-04</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>אלי וינר - ניצחתי</v>
+      </c>
+      <c r="B43" t="str">
+        <v>2026-01-03</v>
+      </c>
+      <c r="C43" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409036&amp;sid=da200abba3294df773d4bbae152092a1</v>
+      </c>
+      <c r="D43" t="str">
+        <v>2026-01-04</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>אבי ריימי &amp; יאיר בודנר מארחים את מוישי רוט - ממקומך</v>
+      </c>
+      <c r="B44" t="str">
+        <v>2026-01-03</v>
+      </c>
+      <c r="C44" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409035&amp;sid=da200abba3294df773d4bbae152092a1</v>
+      </c>
+      <c r="D44" t="str">
+        <v>2026-01-04</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>זהבה - עדיין ילד</v>
+      </c>
+      <c r="B45" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="C45" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409025&amp;sid=da200abba3294df773d4bbae152092a1</v>
+      </c>
+      <c r="D45" t="str">
+        <v>2026-01-04</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>רותם גבאי - שדה חמניה</v>
+      </c>
+      <c r="B46" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="C46" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409024&amp;sid=da200abba3294df773d4bbae152092a1</v>
+      </c>
+      <c r="D46" t="str">
+        <v>2026-01-04</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>ניב אבוטבול - אהבה מטורפת כמוך - 007</v>
+      </c>
+      <c r="B47" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="C47" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409023&amp;sid=da200abba3294df773d4bbae152092a1</v>
+      </c>
+      <c r="D47" t="str">
+        <v>2026-01-04</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>מעיין וגן - תלך כמו גבר</v>
+      </c>
+      <c r="B48" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="C48" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409022&amp;sid=da200abba3294df773d4bbae152092a1</v>
+      </c>
+      <c r="D48" t="str">
+        <v>2026-01-04</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>מושיקו מזרחי - תושיט לי ידיים</v>
+      </c>
+      <c r="B49" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="C49" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409021&amp;sid=da200abba3294df773d4bbae152092a1</v>
+      </c>
+      <c r="D49" t="str">
+        <v>2026-01-04</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>טל ועקנין - השבעתי</v>
+      </c>
+      <c r="B50" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="C50" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409020&amp;sid=da200abba3294df773d4bbae152092a1</v>
+      </c>
+      <c r="D50" t="str">
+        <v>2026-01-04</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>זיו גבאי - אערוך מהלל ניבי</v>
+      </c>
+      <c r="B51" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="C51" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409019&amp;sid=da200abba3294df773d4bbae152092a1</v>
+      </c>
+      <c r="D51" t="str">
+        <v>2026-01-04</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>היוצרים - יאמה</v>
+      </c>
+      <c r="B52" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="C52" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409018&amp;sid=da200abba3294df773d4bbae152092a1</v>
+      </c>
+      <c r="D52" t="str">
+        <v>2026-01-04</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>אלמוג טויטו - אוהב מכל הלב</v>
+      </c>
+      <c r="B53" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="C53" t="str">
         <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409017&amp;sid=da200abba3294df773d4bbae152092a1</v>
       </c>
-      <c r="D27" t="str">
+      <c r="D53" t="str">
         <v>2026-01-04</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D53"/>
   </ignoredErrors>
 </worksheet>
 </file>